--- a/artfynd/S 2080-2024 artfynd.xlsx
+++ b/artfynd/S 2080-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY119"/>
+  <dimension ref="A1:AZ119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110322</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110323</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110327</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110329</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110331</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110333</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110334</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110335</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110336</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110339</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110340</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110341</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110342</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110343</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110345</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110347</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110350</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110351</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110353</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110355</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110356</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110358</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110971</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110974</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110975</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110977</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110791</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3505,6 +3645,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17107165</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3606,6 +3751,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109723</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3707,6 +3857,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109753</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3808,6 +3963,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109759</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3909,6 +4069,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109821</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4010,6 +4175,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109831</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4111,6 +4281,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109833</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4212,6 +4387,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109848</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4313,6 +4493,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109860</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4414,6 +4599,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109864</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4515,6 +4705,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109882</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4616,6 +4811,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109896</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4717,6 +4917,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109913</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4818,6 +5023,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109928</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4919,6 +5129,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109937</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5020,6 +5235,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109939</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5121,6 +5341,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110397</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5222,6 +5447,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110427</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5323,6 +5553,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110434</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5424,6 +5659,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110445</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5525,6 +5765,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110455</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5626,6 +5871,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110462</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5727,6 +5977,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110467</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5828,6 +6083,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110470</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5929,6 +6189,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110473</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6030,6 +6295,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110476</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6131,6 +6401,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110483</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6232,6 +6507,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110492</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6333,6 +6613,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110497</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6434,6 +6719,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110515</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6535,6 +6825,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110520</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6636,6 +6931,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110526</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6737,6 +7037,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110527</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6838,6 +7143,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110533</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6939,6 +7249,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110544</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7040,6 +7355,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110549</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7141,6 +7461,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110557</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7242,6 +7567,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109973</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7341,6 +7671,11 @@
       <c r="AY67" t="inlineStr">
         <is>
           <t>Inventering skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109976</t>
         </is>
       </c>
     </row>
@@ -7437,6 +7772,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110605</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7531,6 +7871,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110607</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7625,6 +7970,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110608</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7719,6 +8069,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110609</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7813,6 +8168,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110610</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7907,6 +8267,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110614</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8001,6 +8366,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110618</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8095,6 +8465,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110620</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8189,6 +8564,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110621</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8290,6 +8670,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110677</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8391,6 +8776,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110678</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8492,6 +8882,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110719</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8593,6 +8988,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110731</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8694,6 +9094,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110733</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8795,6 +9200,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110734</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8896,6 +9306,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110808</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8997,6 +9412,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110814</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9112,6 +9532,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571808</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9227,6 +9652,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571819</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9342,6 +9772,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571843</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9457,6 +9892,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571847</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9572,6 +10012,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571849</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9687,6 +10132,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571863</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9802,6 +10252,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571869</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9917,6 +10372,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571873</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10032,6 +10492,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571876</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10147,6 +10612,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571883</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10262,6 +10732,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571885</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10377,6 +10852,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571886</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10492,6 +10972,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571888</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10607,6 +11092,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571891</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10722,6 +11212,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571901</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10837,6 +11332,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571911</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10952,6 +11452,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571915</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11067,6 +11572,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571932</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11182,6 +11692,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571936</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11297,6 +11812,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571941</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11412,6 +11932,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571942</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11527,6 +12052,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571945</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11642,6 +12172,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571952</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11757,6 +12292,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571962</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11858,6 +12398,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110871</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11959,6 +12504,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110888</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12060,6 +12610,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110889</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12161,6 +12716,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110894</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12262,6 +12822,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110896</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12363,6 +12928,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110906</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12464,6 +13034,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110915</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12565,6 +13140,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110929</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12666,6 +13246,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110942</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12767,6 +13352,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110945</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12868,8 +13458,133 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110946</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>